--- a/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="160">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 7: Pris som konkurransevirkemiddel (V5)</t>
   </si>
@@ -140,18 +140,48 @@
     <t xml:space="preserve">a)  Regn ut priselastisiteten Ep = (ΔM/M) / (ΔP/P): prosentvis endring i antall delt på prosentvis endring i pris. Svar med én desimal og med fortegn.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ep = (ΔM/M) / (ΔP/P): prosentvis endring i mengde delt på prosentvis endring i pris. Tallverdi over 1 er elastisk, under 1 uelastisk (Økonomistyring 2.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mye endrer salgsinntekten seg, i kroner? Salgsinntekt etter minus salgsinntekt før.</t>
   </si>
   <si>
+    <t xml:space="preserve">Salgsinntekt = mengde × pris (STI = M × P, Økonomistyring 8.2). Ved elastisk etterspørsel øker salgsinntekten når prisen settes ned (Økonomistyring 2.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mye endrer det samlede dekningsbidraget seg, i kroner? DB per stykk er pris minus 7 780 kr. Skriv negativt tall hvis det faller.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = pris − variable kostnader per enhet. Samlet DB = DB per enhet × antall (bidragsmetoden, Markedsføring 7.4.1; Økonomistyring 8.2, tabellen nr. 7 og 8).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ida sier: «Etterspørselen er elastisk, altså lønner prisnedsettelsen seg.» Hvilket utsagn er riktig?   A: Ja: elastisk etterspørsel betyr at fortjenesten øker når prisen settes ned   B: Elastisk betyr at salgsinntekten øker; om det lønner seg, avgjør dekningsbidraget   C: Nei: elastisk betyr at salget faller når prisen settes ned   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Skal Kari si ja til Idas forslag? Si hvilket av lærebokas tre mål for prispolitikken Ida følger, når det målet er riktig, og hva som kan skje hvis konkurrentene svarer. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lærebokas mål for prispolitikken: profittmaksimering på lang sikt, salgsmaksimering og status quo (Markedsføring 7.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elastisiteten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengde: (215 − 180) / 180. Pris: (8 400 − 8 830) / 8 830. Del den første på den andre. Fortegnet blir negativt; tallverdien over 1 betyr elastisk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsbidraget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB per stykk = pris − 7 780. Gang med antall, før og etter. Salgsinntekten kan stige mens dekningsbidraget faller.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, innledningen og avsnitt 7.1 (salgsmaksimering og status quo). Priselastisitet: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2.3.1. Ladepunkttallene er de samme som i faktaarket og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -224,9 +254,15 @@
     <t xml:space="preserve">a)  Regn ut driftsmarginen: driftsresultat delt på salgsinntekter, i prosent med én desimal. Det er også det største generelle prisavslaget Fjell tåler før driftsresultatet er null, hvis volum og kostnader står stille.</t>
   </si>
   <si>
+    <t xml:space="preserve">Driftsmargin = driftsresultat × 100 / driftsinntekter (Økonomistyring kap. 4 og Formelsamlingen). At tålt avslag er lik driftsmarginen, gjelder bare når volum og kostnader står stille.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva blir driftsresultatet hvis Fjell setter ned alle prisene 10 % og selger like mye, med de samme kostnadene? Svar i kroner, negativt hvis det blir underskudd.</t>
   </si>
   <si>
+    <t xml:space="preserve">Driftsresultat = driftsinntekter − driftskostnader (Økonomistyring kap. 3 og 9). Med samme volum og kostnader er endringen i driftsresultat lik avslaget i kroner.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvilken markedsform er Fjell i (figur 7.1), og hva betyr det for hvor fritt Mona kan sette prisen?   A: Fullkommen konkurranse: Fjell er mengdetilpasser og må følge kjedens pris   B: Monopolistisk konkurranse: et prisavvik kan holdes hvis kunden ser en forskjell   C: Oligopol: Fjell og kjeden kan bli enige om prisen   (skriv bokstaven)</t>
   </si>
   <si>
@@ -251,6 +287,21 @@
     <t xml:space="preserve">e)  Hva råder du Mona til? Bruk minst ett tall du har regnet, og si hva hun kan gjøre i stedet for å kutte prisen. To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel; bruk driftsmargin og markedsform (Markedsføring 7.1–7.4.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tålt avslag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driftsmargin = 144 240 / 4 795 000. Med samme volum og kostnader går hele avslaget ut av driftsresultatet: 10 % av 4 795 000 er 479 500 kr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intern eller ekstern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intern: Fjells egne kostnader og kvalitet, også slik kunden oppfatter den (7.2). Ekstern: konkurransen, altså hvor mange tilbydere og hvor like tjenestene er (7.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.1 (mål og priskrig), 7.2 (interne arbeidsbetingelser), 7.3 med figur 7.1 (markedsformer) og 7.4.2 (konkurransebasert prissetting). Fjells budsjett: Økonomistyring kap. 9 (OK09). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -308,18 +359,42 @@
     <t xml:space="preserve">a)  Hva blir dekningsbidraget per skap etter 10 % rabatt? Ny pris minus de variable kostnadene. Svar i kroner med to desimaler.</t>
   </si>
   <si>
+    <t xml:space="preserve">DB per enhet = pris − variable kostnader (Markedsføring 7.4.1; Økonomistyring 8.2). DG = DB × 100 / pris (Økonomistyring 8.2, nr. 10).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange prosent flere skap må Nordlys selge for å ha like mye dekningsbidrag som uten rabatt? Volumfaktor = gammelt DB / nytt DB; volumøkningen er faktoren minus 1. Svar i hele prosent.</t>
   </si>
   <si>
+    <t xml:space="preserve">Samme samlede DB: gammelt DB × gammel mengde = nytt DB × ny mengde. Volumkravet står ikke i boka; det følger av bidragsmetoden (Markedsføring 7.4.1) og DB totalt = DB per enhet × M (Økonomistyring 8.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mye er igjen over selvkost per skap etter rabatten? Ny pris minus selvkost, i kroner med to desimaler.</t>
   </si>
   <si>
+    <t xml:space="preserve">Selvkost = faste + variable kostnader; pris = selvkost + fortjeneste (selvkostmetoden, Markedsføring 7.4.1; Økonomistyring kap. 5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ronny sier: «Ti prosent rabatt? Da må vi bare selge ti prosent flere skap for å tjene det samme.» Hvilket svar er riktig?   A: Ronny har rett: 10 % lavere pris krever 10 % mer salg   B: Det må 37,7 % flere skap til, fordi DB faller 37,7 %   C: Det må 61 % flere skap til, fordi rabatten tas fra DB, ikke fra prisen   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva skal Ida svare styrelederen? Gi et motbud som er prisdifferensiering etter et av lærebokas kriterier (7.5), ikke bare en lavere pris. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Prisdifferensiering: ulik pris for samme produkt når minst ett kriterium er innfridd; rabattformene kvantums-, kontant- og funksjonsrabatt (Markedsføring 7.5 og 7.5.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nytt dekningsbidrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny pris = 26 611,20 × 0,90. Trekk fra 19 560. De indirekte kostnadene på 4 200 skal ikke trekkes fra: det er dem dekningsbidraget skal dekke.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volumkravet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gammelt DB / nytt DB = 7 051,20 / 4 390,08. Trekk fra 1 og gang med 100. Regn av dekningsbidraget, ikke av prisen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (selvkost- og bidragsmetoden), 7.4.2 og 7.5.4 (rabatter). Kalkylen: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 5 (OK05). Volumkravet følger av bidragsmetoden. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -377,12 +452,21 @@
     <t xml:space="preserve">a)  Hva er prisen per lader uten mva og uten rabatt? Tre timer à 890 kr pluss materiellet med 20 % påslag.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pris i oppdragskalkylen = timer × timepris + materiell × (1 + påslag) (Økonomistyring kap. 5, bidragskalkyle for tjeneste). DB = pris − variable kostnader (Markedsføring 7.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva blir dekningsbidraget per lader med 10 % rabatt? Ny pris minus variable kostnader på 9 770 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nytt DB = pris × (1 − rabatt) − variable kostnader (bidragsmetoden, Markedsføring 7.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mange ladere måtte Fjell montert med 10 % rabatt for å få like mye dekningsbidrag som 12 ladere til full pris? Rund opp til helt antall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nødvendig antall = samlet DB uten rabatt / nytt DB per enhet, rundet opp (følger av DB totalt = DB per enhet × M, Økonomistyring 8.2; ikke en egen formel i boka).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona har fem ideer. Hvilke av dem er prisdifferensiering etter et av lærebokas kriterier (7.5), og hvilke er bare en lavere pris? Svar ja eller nei for hver.</t>
   </si>
   <si>
@@ -402,6 +486,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilket motbud skal Mona gi styret i stedet for 10 %? Bruk ett tall du har regnet, og si hvilket kriterium for prisdifferensiering motbudet bygger på. To setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisdifferensiering med kvantums-, kontant- eller funksjonsrabatt (Markedsføring 7.5.4), regnet med bidragsmetoden (7.4.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris og DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris = 3 × 890 + 8 000 × 1,20. Variable kostnader = 3 × 590 + 8 000 = 9 770. Med rabatt: pris × 0,90 − 9 770.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kriteriene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seks kriterier (7.5): sted, kjøpstidspunkt, alder, mengde, betalingstidspunkt, kunden gjør noe selv. Kjøper, betaler eller gjør kunden noe annerledes? Hvis ikke, er det bare lavere pris.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (bidragsmetoden) og 7.5 med 7.5.4 (kriteriene for prisdifferensiering og rabattformene). Fjells oppdragskalkyle: OK05 og OK07 (590 kr per montørtime, 20 % påslag på materiell). Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -415,7 +514,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -482,8 +581,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,13 +620,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -558,7 +697,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -627,11 +766,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,8 +835,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -691,7 +850,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -705,7 +864,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1008,7 +1167,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1158,35 +1317,20 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="16" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(216600))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(-55700))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
         <v>40</v>
       </c>
@@ -1194,84 +1338,195 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(216600))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="16" t="str">
+        <f aca="false">IF(F23="","",IF(ABS(F23-(-55700))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
     </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1288,7 +1543,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1299,7 +1554,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1309,7 +1564,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1320,7 +1575,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1331,10 +1586,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -1343,11 +1598,11 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>49</v>
+      <c r="A8" s="24" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1356,11 +1611,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>51</v>
+      <c r="A9" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1369,11 +1624,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>53</v>
+      <c r="A10" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1382,11 +1637,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>55</v>
+      <c r="A11" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1395,11 +1650,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>57</v>
+      <c r="A12" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1408,11 +1663,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>59</v>
+      <c r="A13" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1421,11 +1676,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>61</v>
+      <c r="A14" s="24" t="s">
+        <v>71</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1434,11 +1689,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>63</v>
+      <c r="A15" s="24" t="s">
+        <v>73</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1463,7 +1718,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1475,173 +1730,249 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(-335260))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F21" s="14"/>
+      <c r="G21" s="16" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(-335260))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="16" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="17"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="16" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="16" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="16" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="42" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1655,18 +1986,24 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1683,7 +2020,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1694,7 +2031,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,7 +2041,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1715,7 +2052,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1726,27 +2063,27 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>83</v>
+        <v>99</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>19560</v>
@@ -1757,16 +2094,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>86</v>
+        <v>102</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="C10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>4200</v>
@@ -1777,7 +2114,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>23760</v>
@@ -1788,21 +2125,21 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>90</v>
+        <v>106</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>107</v>
       </c>
       <c r="C13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="20"/>
+        <v>108</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
@@ -1832,7 +2169,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1844,120 +2181,216 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(61))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(190.08))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="C","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(61))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(190.08))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>115</v>
+      </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1974,7 +2407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1985,7 +2418,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1995,7 +2428,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2006,7 +2439,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2017,10 +2450,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -2029,11 +2462,11 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>102</v>
+      <c r="A8" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2042,11 +2475,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>104</v>
+      <c r="A9" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2055,11 +2488,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>106</v>
+      <c r="A10" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2068,11 +2501,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>108</v>
+      <c r="A11" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2081,11 +2514,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>110</v>
+      <c r="A12" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2094,11 +2527,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>112</v>
+      <c r="A13" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2107,11 +2540,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>114</v>
+      <c r="A14" s="24" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2136,7 +2569,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2148,173 +2581,262 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="16" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(1273))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(24))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F20" s="14"/>
+      <c r="G20" s="16" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(1273))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="16" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(ABS(F23-(24))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="16" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="16" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2327,18 +2849,25 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
@@ -92,10 +92,10 @@
     <t xml:space="preserve">25 minutter · Helst alene. Sammen med sidemannen eller flere hvis du vil. Ark og blyant, appen (PC eller mobil) eller læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Prisen påvirker etterspørselen, etterspørselen bestemmer salgsinntekten, og salgsinntekten påvirker fortjenesten (kap. 7, innledningen). Priselastisiteten Ep er prosentvis endring i mengde delt på prosentvis endring i pris (Økonomistyring kap. 2.3.1). Er tallverdien over 1, er etterspørselen elastisk, og salgsinntekten øker når prisen settes ned. Men elastisiteten sier ingenting om fortjenesten: det avgjør dekningsbidraget. Samlet DB = (pris − variable kostnader per stykk) × antall.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Delmålet i markedsplanen er 215 ladepunkt i år (Markedsføring kap. 3). Ida tror ikke det nås til dagens pris, 8 830 kr uten mva; da regner hun med 180, som i fjor. Hun foreslår å sette prisen ned til 8 400 kr og anslår at salget da blir 215. Et ladepunkt koster Nordlys 7 780 kr i variable kostnader: materiell 6 500 kr og 2 montørtimer à 640 kr. Gå fram slik: prosentvis endring i mengde og i pris, så elastisiteten, så salgsinntekten før og etter, og til slutt det samlede dekningsbidraget før og etter. Først da vet Kari om forslaget lønner seg.</t>
+    <t xml:space="preserve">Kort oppsummert: Prisen påvirker etterspørselen, etterspørselen bestemmer salgsinntekten, og salgsinntekten påvirker fortjenesten (kap. 7, innledningen). Priselastisiteten er prosentvis endring i mengde delt på prosentvis endring i pris (Økonomistyring kap. 2.3.1). Er tallverdien over 1, er etterspørselen elastisk, og salgsinntekten øker når prisen settes ned. Men elastisiteten sier ingenting om fortjenesten: det avgjør dekningsbidraget. Samlet dekningsbidrag = (pris − variable kostnader per stykk) × antall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Delmålet i markedsplanen er 215 ladepunkt i år (Markedsføring kap. 3). Ida tror ikke det nås til dagens pris, 8 830 kr uten merverdiavgift; da regner hun med 180, som i fjor. Hun foreslår å sette prisen ned til 8 400 kr og anslår at salget da blir 215. Et ladepunkt koster Nordlys 7 780 kr i variable kostnader: materiell 6 500 kr og 2 montørtimer à 640 kr. Gå fram slik: prosentvis endring i mengde og i pris, så elastisiteten, så salgsinntekten før og etter, og til slutt det samlede dekningsbidraget før og etter. Først da vet Kari om forslaget lønner seg.</t>
   </si>
   <si>
     <t xml:space="preserve">Ladepunkt</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Idas forslag</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris per ladepunkt, kr uten mva</t>
+    <t xml:space="preserve">Pris per ladepunkt, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Antall i år (Idas anslag)</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">Sjekk</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Regn ut priselastisiteten Ep = (ΔM/M) / (ΔP/P): prosentvis endring i antall delt på prosentvis endring i pris. Svar med én desimal og med fortegn.</t>
+    <t xml:space="preserve">a)  Regn ut priselastisiteten: prosentvis endring i antall delt på prosentvis endring i pris. Svar med én desimal og med fortegn.</t>
   </si>
   <si>
     <t xml:space="preserve">Formel og begrep</t>
   </si>
   <si>
-    <t xml:space="preserve">Ep = (ΔM/M) / (ΔP/P): prosentvis endring i mengde delt på prosentvis endring i pris. Tallverdi over 1 er elastisk, under 1 uelastisk (Økonomistyring 2.3.1).</t>
+    <t xml:space="preserve">Priselastisitet = prosentvis endring i mengde / prosentvis endring i pris. Tallverdi over 1 er elastisk, under 1 uelastisk (Økonomistyring 2.3.1).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvor mye endrer salgsinntekten seg, i kroner? Salgsinntekt etter minus salgsinntekt før.</t>
   </si>
   <si>
-    <t xml:space="preserve">Salgsinntekt = mengde × pris (STI = M × P, Økonomistyring 8.2). Ved elastisk etterspørsel øker salgsinntekten når prisen settes ned (Økonomistyring 2.3.1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)  Hvor mye endrer det samlede dekningsbidraget seg, i kroner? DB per stykk er pris minus 7 780 kr. Skriv negativt tall hvis det faller.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB per enhet = pris − variable kostnader per enhet. Samlet DB = DB per enhet × antall (bidragsmetoden, Markedsføring 7.4.1; Økonomistyring 8.2, tabellen nr. 7 og 8).</t>
+    <t xml:space="preserve">Salgsinntekt = mengde × pris (Økonomistyring 8.2). Ved elastisk etterspørsel øker salgsinntekten når prisen settes ned (Økonomistyring 2.3.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)  Hvor mye endrer det samlede dekningsbidraget seg, i kroner? Dekningsbidraget per stykk er pris minus 7 780 kr. Skriv negativt tall hvis det faller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader per enhet. Samlet dekningsbidrag = dekningsbidrag per enhet × antall (bidragsmetoden, Markedsføring 7.4.1; Økonomistyring 8.2, tabellen nr. 7 og 8).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Ida sier: «Etterspørselen er elastisk, altså lønner prisnedsettelsen seg.» Hvilket utsagn er riktig?   A: Ja: elastisk etterspørsel betyr at fortjenesten øker når prisen settes ned   B: Elastisk betyr at salgsinntekten øker; om det lønner seg, avgjør dekningsbidraget   C: Nei: elastisk betyr at salget faller når prisen settes ned   (skriv bokstaven)</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">Dekningsbidraget</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per stykk = pris − 7 780. Gang med antall, før og etter. Salgsinntekten kan stige mens dekningsbidraget faller.</t>
+    <t xml:space="preserve">Dekningsbidrag per stykk = pris − 7 780. Gang med antall, før og etter. Salgsinntekten kan stige mens dekningsbidraget faller.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, innledningen og avsnitt 7.1 (salgsmaksimering og status quo). Priselastisitet: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2.3.1. Ladepunkttallene er de samme som i faktaarket og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">Intern: Fjells egne kostnader og kvalitet, også slik kunden oppfatter den (7.2). Ekstern: konkurransen, altså hvor mange tilbydere og hvor like tjenestene er (7.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.1 (mål og priskrig), 7.2 (interne arbeidsbetingelser), 7.3 med figur 7.1 (markedsformer) og 7.4.2 (konkurransebasert prissetting). Fjells budsjett: Økonomistyring kap. 9 (OK09). Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.1 (mål og priskrig), 7.2 (interne arbeidsbetingelser), 7.3 med figur 7.1 (markedsformer) og 7.4.2 (konkurransebasert prissetting). Fjells budsjett: Økonomistyring kap. 9. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: «Ti prosent, så signerer jeg i dag»</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: En rabatt endrer prisen, men ikke de variable kostnadene. Derfor tas hele rabatten fra dekningsbidraget. Nytt DB = pris × (1 − rabatt) − variable kostnader. Hvor mye mer som må selges for å ha like mye dekningsbidrag som før: volumfaktor = gammelt DB / nytt DB, og volumøkningen er faktoren minus 1. Selvkost er gulvet på lang sikt, de variable kostnadene det absolutte gulvet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Styrelederen i et borettslag skal ha byttet sikringsskapet i en leilighet, og borettslaget har flere leiligheter som skal gjøres de neste tre årene. Han har fått Nordlys' tilbud og sier: «Ti prosent, så signerer jeg i dag.» Idas kalkyle er den samme som i Økonomistyring kap. 5: direkte kostnader 19 560 kr (14 montørtimer à 640 kr, materiell 9 800 kr, kjøring 800 kr), indirekte kostnader 4 200 kr, selvkost 23 760 kr, 12 % fortjeneste, pris 26 611,20 kr uten mva. De direkte kostnadene er de variable. Styrelederen har også to tilbud fra konkurrenter: 30 500 og 35 900 kr inkl. mva. Gå fram slik: ny pris og nytt dekningsbidrag, så volumkravet, så hva som er igjen over selvkost. Til slutt: hva Ida skal svare.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sikringsskap, kr uten mva</t>
+    <t xml:space="preserve">Kort oppsummert: En rabatt endrer prisen, men ikke de variable kostnadene. Derfor tas hele rabatten fra dekningsbidraget. Nytt dekningsbidrag = pris × (1 − rabatt) − variable kostnader. Hvor mye mer som må selges for å ha like mye dekningsbidrag som før: volumfaktor = gammelt dekningsbidrag / nytt dekningsbidrag, og volumøkningen er faktoren minus 1. Selvkost er gulvet på lang sikt, de variable kostnadene det absolutte gulvet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Styrelederen i et borettslag skal ha byttet sikringsskapet i en leilighet, og borettslaget har flere leiligheter som skal gjøres de neste tre årene. Han har fått Nordlys' tilbud og sier: «Ti prosent, så signerer jeg i dag.» Idas kalkyle er den samme som i Økonomistyring kap. 5: direkte kostnader 19 560 kr (14 montørtimer à 640 kr, materiell 9 800 kr, kjøring 800 kr), indirekte kostnader 4 200 kr, selvkost 23 760 kr, 12 % fortjeneste, pris 26 611,20 kr uten merverdiavgift. De direkte kostnadene er de variable. Styrelederen har også to tilbud fra konkurrenter: 30 500 og 35 900 kr inkludert merverdiavgift. Gå fram slik: ny pris og nytt dekningsbidrag, så volumkravet, så hva som er igjen over selvkost. Til slutt: hva Ida skal svare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sikringsskap, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Tilbudet</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">2 851,20</t>
   </si>
   <si>
-    <t xml:space="preserve">Konkurrenttilbud inkl. mva</t>
+    <t xml:space="preserve">Konkurrenttilbud med merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">30 500 og 35 900</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">a)  Hva blir dekningsbidraget per skap etter 10 % rabatt? Ny pris minus de variable kostnadene. Svar i kroner med to desimaler.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB per enhet = pris − variable kostnader (Markedsføring 7.4.1; Økonomistyring 8.2). DG = DB × 100 / pris (Økonomistyring 8.2, nr. 10).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)  Hvor mange prosent flere skap må Nordlys selge for å ha like mye dekningsbidrag som uten rabatt? Volumfaktor = gammelt DB / nytt DB; volumøkningen er faktoren minus 1. Svar i hele prosent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samme samlede DB: gammelt DB × gammel mengde = nytt DB × ny mengde. Volumkravet står ikke i boka; det følger av bidragsmetoden (Markedsføring 7.4.1) og DB totalt = DB per enhet × M (Økonomistyring 8.2).</t>
+    <t xml:space="preserve">Dekningsbidrag per enhet = pris − variable kostnader (Markedsføring 7.4.1; Økonomistyring 8.2). Dekningsgrad = dekningsbidrag × 100 / pris (Økonomistyring 8.2, nr. 10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)  Hvor mange prosent flere skap må Nordlys selge for å ha like mye dekningsbidrag som uten rabatt? Volumfaktor = gammelt dekningsbidrag / nytt dekningsbidrag; volumøkningen er faktoren minus 1. Svar i hele prosent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samme samlede dekningsbidrag: gammelt dekningsbidrag × gammel mengde = nytt dekningsbidrag × ny mengde. Volumkravet står ikke i boka; det følger av bidragsmetoden (Markedsføring 7.4.1) og samlet dekningsbidrag = dekningsbidrag per enhet × mengde (Økonomistyring 8.2).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Hvor mye er igjen over selvkost per skap etter rabatten? Ny pris minus selvkost, i kroner med to desimaler.</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">Selvkost = faste + variable kostnader; pris = selvkost + fortjeneste (selvkostmetoden, Markedsføring 7.4.1; Økonomistyring kap. 5).</t>
   </si>
   <si>
-    <t xml:space="preserve">d)  Ronny sier: «Ti prosent rabatt? Da må vi bare selge ti prosent flere skap for å tjene det samme.» Hvilket svar er riktig?   A: Ronny har rett: 10 % lavere pris krever 10 % mer salg   B: Det må 37,7 % flere skap til, fordi DB faller 37,7 %   C: Det må 61 % flere skap til, fordi rabatten tas fra DB, ikke fra prisen   (skriv bokstaven)</t>
+    <t xml:space="preserve">d)  Ronny sier: «Ti prosent rabatt? Da må vi bare selge ti prosent flere skap for å tjene det samme.» Hvilket svar er riktig?   A: Ronny har rett: 10 % lavere pris krever 10 % mer salg   B: Det må 37,7 % flere skap til, fordi dekningsbidraget faller 37,7 %   C: Det må 61 % flere skap til, fordi rabatten tas fra dekningsbidraget, ikke fra prisen   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva skal Ida svare styrelederen? Gi et motbud som er prisdifferensiering etter et av lærebokas kriterier (7.5), ikke bare en lavere pris. To–tre setninger.</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">Volumkravet</t>
   </si>
   <si>
-    <t xml:space="preserve">Gammelt DB / nytt DB = 7 051,20 / 4 390,08. Trekk fra 1 og gang med 100. Regn av dekningsbidraget, ikke av prisen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (selvkost- og bidragsmetoden), 7.4.2 og 7.5.4 (rabatter). Kalkylen: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 5 (OK05). Volumkravet følger av bidragsmetoden. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Gammelt dekningsbidrag / nytt dekningsbidrag = 7 051,20 / 4 390,08. Trekk fra 1 og gang med 100. Regn av dekningsbidraget, ikke av prisen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (selvkost- og bidragsmetoden), 7.4.2 og 7.5.4 (rabatter). Kalkylen: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 5. Volumkravet følger av bidragsmetoden. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Fjell Elektro: 12 elbilladere og 10 % rabatt</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">Timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr uten mva</t>
+    <t xml:space="preserve">890 kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Materiell</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">36 montørtimer, plass i kalenderen neste måned</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Hva er prisen per lader uten mva og uten rabatt? Tre timer à 890 kr pluss materiellet med 20 % påslag.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pris i oppdragskalkylen = timer × timepris + materiell × (1 + påslag) (Økonomistyring kap. 5, bidragskalkyle for tjeneste). DB = pris − variable kostnader (Markedsføring 7.4.1).</t>
+    <t xml:space="preserve">a)  Hva er prisen per lader uten merverdiavgift og uten rabatt? Tre timer à 890 kr pluss materiellet med 20 % påslag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris i oppdragskalkylen = timer × timepris + materiell × (1 + påslag) (Økonomistyring kap. 5, bidragskalkyle for tjeneste). Dekningsbidrag = pris − variable kostnader (Markedsføring 7.4.1).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hva blir dekningsbidraget per lader med 10 % rabatt? Ny pris minus variable kostnader på 9 770 kr.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nytt DB = pris × (1 − rabatt) − variable kostnader (bidragsmetoden, Markedsføring 7.4.1).</t>
+    <t xml:space="preserve">Nytt dekningsbidrag = pris × (1 − rabatt) − variable kostnader (bidragsmetoden, Markedsføring 7.4.1).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Hvor mange ladere måtte Fjell montert med 10 % rabatt for å få like mye dekningsbidrag som 12 ladere til full pris? Rund opp til helt antall.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nødvendig antall = samlet DB uten rabatt / nytt DB per enhet, rundet opp (følger av DB totalt = DB per enhet × M, Økonomistyring 8.2; ikke en egen formel i boka).</t>
+    <t xml:space="preserve">Nødvendig antall = samlet dekningsbidrag uten rabatt / nytt dekningsbidrag per enhet, rundet opp (følger av samlet dekningsbidrag = dekningsbidrag per enhet × mengde, Økonomistyring 8.2; ikke en egen formel i boka).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Mona har fem ideer. Hvilke av dem er prisdifferensiering etter et av lærebokas kriterier (7.5), og hvilke er bare en lavere pris? Svar ja eller nei for hver.</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">Prisdifferensiering med kvantums-, kontant- eller funksjonsrabatt (Markedsføring 7.5.4), regnet med bidragsmetoden (7.4.1).</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris og DB</t>
+    <t xml:space="preserve">Pris og dekningsbidrag</t>
   </si>
   <si>
     <t xml:space="preserve">Pris = 3 × 890 + 8 000 × 1,20. Variable kostnader = 3 × 590 + 8 000 = 9 770. Med rabatt: pris × 0,90 − 9 770.</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">Seks kriterier (7.5): sted, kjøpstidspunkt, alder, mengde, betalingstidspunkt, kunden gjør noe selv. Kjøper, betaler eller gjør kunden noe annerledes? Hvis ikke, er det bare lavere pris.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (bidragsmetoden) og 7.5 med 7.5.4 (kriteriene for prisdifferensiering og rabattformene). Fjells oppdragskalkyle: OK05 og OK07 (590 kr per montørtime, 20 % påslag på materiell). Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 7, avsnitt 7.4.1 (bidragsmetoden) og 7.5 med 7.5.4 (kriteriene for prisdifferensiering og rabattformene). Fjells oppdragskalkyle: Økonomistyring kap. 5 og 7 (590 kr per montørtime, 20 % påslag på materiell). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
         <v>38</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
         <v>38</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
         <v>38</v>
       </c>

--- a/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="160">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 7: Pris som konkurransevirkemiddel (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 7: Pris som konkurransevirkemiddel (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma07/MA07_Klasseoppgaver_v5.xlsx
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Driftskostnader i fjor</t>
   </si>
   <si>
-    <t xml:space="preserve">4 650 760 kr til sammen</t>
+    <t xml:space="preserve">4 650 760 kr (4 795 000 − 144 240)</t>
   </si>
   <si>
     <t xml:space="preserve">Driftsresultat i fjor</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">Variable kostnader per lader</t>
   </si>
   <si>
-    <t xml:space="preserve">3 × 590 + 8 000 = 9 770 kr</t>
+    <t xml:space="preserve">3 × 590 kr (lønn per time) + 8 000 = 9 770 kr</t>
   </si>
   <si>
     <t xml:space="preserve">Styrets krav</t>
